--- a/Data Analysis & AI/tests_diagnose/Data/normal ranges.xlsx
+++ b/Data Analysis & AI/tests_diagnose/Data/normal ranges.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lenovo\EMAN\1.1.1 Graduation\Graduation-Project\Data Analysis &amp; AI\tests_diagnose\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B607BDED-11D4-4308-9C3F-B9532EDAC6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D31B1DF-7EE8-497D-9E5C-6A1F4B4DEBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BD5E39A0-6F15-4585-B47B-C3FEFEB75A9E}"/>
   </bookViews>
@@ -820,7 +820,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -849,6 +849,12 @@
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1457,16 +1463,16 @@
       </c>
     </row>
     <row r="12" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="19" t="s">
         <v>44</v>
       </c>
     </row>

--- a/Data Analysis & AI/tests_diagnose/Data/normal ranges.xlsx
+++ b/Data Analysis & AI/tests_diagnose/Data/normal ranges.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lenovo\EMAN\1.1.1 Graduation\Graduation-Project\Data Analysis &amp; AI\tests_diagnose\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lenovo\EMAN\1.1.1 Graduation\New_GIthub\Graduation-Project\Data Analysis &amp; AI\tests_diagnose\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D31B1DF-7EE8-497D-9E5C-6A1F4B4DEBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8473280D-2E7E-4E12-94D5-10AD103BFECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{BD5E39A0-6F15-4585-B47B-C3FEFEB75A9E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{BD5E39A0-6F15-4585-B47B-C3FEFEB75A9E}"/>
   </bookViews>
   <sheets>
     <sheet name="ABO &amp; RH-FactorBlood Type_x0009_Antig" sheetId="1" r:id="rId1"/>
     <sheet name="CBC" sheetId="2" r:id="rId2"/>
     <sheet name="HbA1c" sheetId="3" r:id="rId3"/>
-    <sheet name="Urinalysis" sheetId="4" r:id="rId4"/>
-    <sheet name="Hepatitis B" sheetId="5" r:id="rId5"/>
-    <sheet name="Ferritin" sheetId="6" r:id="rId6"/>
-    <sheet name="TSH" sheetId="7" r:id="rId7"/>
+    <sheet name="FBG" sheetId="8" r:id="rId4"/>
+    <sheet name="Urinalysis" sheetId="4" r:id="rId5"/>
+    <sheet name="Hepatitis B" sheetId="5" r:id="rId6"/>
+    <sheet name="Ferritin" sheetId="6" r:id="rId7"/>
+    <sheet name="TSH" sheetId="7" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="219">
   <si>
     <t>Blood Type</t>
   </si>
@@ -679,6 +680,15 @@
   </si>
   <si>
     <t>$15 - 150$</t>
+  </si>
+  <si>
+    <t>Less than 100</t>
+  </si>
+  <si>
+    <t>100 to 125</t>
+  </si>
+  <si>
+    <t>&gt;126</t>
   </si>
 </sst>
 </file>
@@ -746,7 +756,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -780,6 +790,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -820,7 +836,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -855,6 +871,7 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1864,6 +1881,69 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97FC50D6-0514-436D-B0FB-3A6BF92EE1BF}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="99.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="31.2" x14ac:dyDescent="0.6">
+      <c r="B1" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" t="s">
+        <v>216</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93AEADBA-1493-4360-BB37-790418A234BA}">
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultColWidth="29.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1891,7 +1971,7 @@
       <c r="D2" s="12"/>
       <c r="E2" s="12"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>97</v>
       </c>
@@ -1911,7 +1991,7 @@
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>101</v>
       </c>
@@ -2022,7 +2102,7 @@
       <c r="D13" s="10"/>
       <c r="E13" s="10"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>115</v>
       </c>
@@ -2035,7 +2115,7 @@
       <c r="D14" s="10"/>
       <c r="E14" s="10"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>116</v>
       </c>
@@ -2048,7 +2128,7 @@
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>117</v>
       </c>
@@ -2061,7 +2141,7 @@
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>119</v>
       </c>
@@ -2084,19 +2164,19 @@
       <c r="E18" s="10"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
+      <c r="A19" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="B19" s="17" t="s">
+      <c r="B19" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="C19" s="17" t="s">
+      <c r="C19" s="10" t="s">
         <v>124</v>
       </c>
       <c r="D19" s="10"/>
       <c r="E19" s="10"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>125</v>
       </c>
@@ -2109,7 +2189,7 @@
       <c r="D20" s="10"/>
       <c r="E20" s="10"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>127</v>
       </c>
@@ -2122,7 +2202,7 @@
       <c r="D21" s="10"/>
       <c r="E21" s="10"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>129</v>
       </c>
@@ -2135,7 +2215,7 @@
       <c r="D22" s="10"/>
       <c r="E22" s="10"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>131</v>
       </c>
@@ -2153,7 +2233,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{561FB6A5-6B27-401A-80EA-1B58D3E12CDE}">
   <dimension ref="A1:D19"/>
   <sheetFormatPr defaultColWidth="76.21875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2287,7 +2367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949305DD-9E85-4CC5-840F-D00C96CA734D}">
   <dimension ref="A1:E28"/>
   <sheetFormatPr defaultColWidth="24" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2498,7 +2578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C47CCD34-1D93-4729-A3AD-CAEACE0324F8}">
   <dimension ref="A1:E30"/>
   <sheetFormatPr defaultColWidth="20" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Data Analysis & AI/tests_diagnose/Data/normal ranges.xlsx
+++ b/Data Analysis & AI/tests_diagnose/Data/normal ranges.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\lenovo\EMAN\1.1.1 Graduation\New_GIthub\Graduation-Project\Data Analysis &amp; AI\tests_diagnose\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8473280D-2E7E-4E12-94D5-10AD103BFECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC07674-7182-4D0D-A253-5EE44CEBB403}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{BD5E39A0-6F15-4585-B47B-C3FEFEB75A9E}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="220">
   <si>
     <t>Blood Type</t>
   </si>
@@ -689,6 +689,9 @@
   </si>
   <si>
     <t>&gt;126</t>
+  </si>
+  <si>
+    <t>FBG Ranges</t>
   </si>
 </sst>
 </file>
@@ -1899,7 +1902,7 @@
         <v>78</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>81</v>
